--- a/data/trans_orig/P1001-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1001-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2007</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12198</t>
+          <t>13074</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30940</t>
+          <t>31456</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12980</t>
+          <t>13447</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30797</t>
+          <t>30858</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29350</t>
+          <t>30018</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55471</t>
+          <t>55516</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>442836</t>
+          <t>442320</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>461578</t>
+          <t>460702</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>275883</t>
+          <t>275822</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>293700</t>
+          <t>293233</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>724986</t>
+          <t>724941</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>751107</t>
+          <t>750439</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9139</t>
+          <t>9474</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25656</t>
+          <t>26445</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21936</t>
+          <t>21775</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43817</t>
+          <t>43064</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34985</t>
+          <t>34550</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63438</t>
+          <t>62108</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>341278</t>
+          <t>340489</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>357795</t>
+          <t>357460</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>328048</t>
+          <t>328801</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>349929</t>
+          <t>350090</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>675361</t>
+          <t>676691</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>703814</t>
+          <t>704249</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24423</t>
+          <t>24064</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46798</t>
+          <t>46234</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11409</t>
+          <t>11943</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27853</t>
+          <t>28558</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38386</t>
+          <t>39920</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68224</t>
+          <t>66705</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>495591</t>
+          <t>496155</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517966</t>
+          <t>518325</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>139929</t>
+          <t>139224</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156373</t>
+          <t>155839</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>641947</t>
+          <t>643466</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>671785</t>
+          <t>670251</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,38%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77125</t>
+          <t>78266</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>113106</t>
+          <t>116088</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55345</t>
+          <t>53179</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>86881</t>
+          <t>85136</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>142438</t>
+          <t>140323</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>189540</t>
+          <t>188045</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1125228</t>
+          <t>1122246</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1161209</t>
+          <t>1160068</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>627404</t>
+          <t>629149</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>658940</t>
+          <t>661106</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1763080</t>
+          <t>1764575</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1810182</t>
+          <t>1812297</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,81%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33101</t>
+          <t>32178</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43378</t>
+          <t>41441</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71844</t>
+          <t>70328</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60147</t>
+          <t>60605</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96024</t>
+          <t>96219</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>317454</t>
+          <t>318377</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>336701</t>
+          <t>336946</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>496908</t>
+          <t>498424</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>525374</t>
+          <t>527311</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>823283</t>
+          <t>823088</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>859160</t>
+          <t>858702</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,41%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5830</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18705</t>
+          <t>19383</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>102590</t>
+          <t>99427</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>145813</t>
+          <t>141364</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>111575</t>
+          <t>110534</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>156158</t>
+          <t>154325</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279496</t>
+          <t>278818</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>292371</t>
+          <t>292513</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1102947</t>
+          <t>1107396</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1146170</t>
+          <t>1149333</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1390802</t>
+          <t>1392635</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1435385</t>
+          <t>1436426</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,85%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>172708</t>
+          <t>171777</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>227186</t>
+          <t>227853</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>283907</t>
+          <t>286896</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>352337</t>
+          <t>356246</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>472093</t>
+          <t>475504</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>559457</t>
+          <t>559871</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3043004</t>
+          <t>3042337</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3097482</t>
+          <t>3098413</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3025787</t>
+          <t>3021878</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3094217</t>
+          <t>3091228</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6088857</t>
+          <t>6088443</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6176221</t>
+          <t>6172810</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,85%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2012</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11339</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30718</t>
+          <t>29620</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15191</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34107</t>
+          <t>34800</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30603</t>
+          <t>29572</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58395</t>
+          <t>56562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>405556</t>
+          <t>406654</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>424935</t>
+          <t>425535</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>280347</t>
+          <t>279654</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>299263</t>
+          <t>300003</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>692333</t>
+          <t>694166</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>720125</t>
+          <t>721156</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17432</t>
+          <t>18692</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41154</t>
+          <t>41938</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20442</t>
+          <t>20938</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44033</t>
+          <t>43422</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42155</t>
+          <t>42931</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73207</t>
+          <t>73099</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>377643</t>
+          <t>376859</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>401365</t>
+          <t>400105</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>293978</t>
+          <t>294589</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>317569</t>
+          <t>317073</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>683601</t>
+          <t>683709</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>714653</t>
+          <t>713877</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40007</t>
+          <t>39553</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71247</t>
+          <t>70731</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35106</t>
+          <t>35764</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61054</t>
+          <t>61219</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82250</t>
+          <t>81917</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>124581</t>
+          <t>121799</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>558168</t>
+          <t>558684</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>589408</t>
+          <t>589862</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>199075</t>
+          <t>198910</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>225023</t>
+          <t>224365</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>764963</t>
+          <t>767745</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>807294</t>
+          <t>807627</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,79%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85473</t>
+          <t>85428</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>126722</t>
+          <t>127164</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77275</t>
+          <t>76133</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116182</t>
+          <t>114327</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>170059</t>
+          <t>170750</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>228826</t>
+          <t>228417</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1032287</t>
+          <t>1031845</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1073536</t>
+          <t>1073581</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>650475</t>
+          <t>652330</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>689382</t>
+          <t>690524</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1696841</t>
+          <t>1697250</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1755608</t>
+          <t>1754917</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,13%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19247</t>
+          <t>19142</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40825</t>
+          <t>40941</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>128951</t>
+          <t>129036</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>173249</t>
+          <t>175414</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>154756</t>
+          <t>156990</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>206502</t>
+          <t>210670</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>468717</t>
+          <t>468601</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>490295</t>
+          <t>490400</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>586273</t>
+          <t>584108</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>630571</t>
+          <t>630486</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1062562</t>
+          <t>1058394</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1114308</t>
+          <t>1112074</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,63%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18736</t>
+          <t>18039</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>151316</t>
+          <t>150615</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>197755</t>
+          <t>197665</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>158193</t>
+          <t>157293</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>208856</t>
+          <t>206974</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248146</t>
+          <t>248843</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261996</t>
+          <t>262062</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>911596</t>
+          <t>911686</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>958035</t>
+          <t>958736</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1167377</t>
+          <t>1169259</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1218040</t>
+          <t>1218940</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,57%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>207853</t>
+          <t>212293</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>272174</t>
+          <t>276493</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>475477</t>
+          <t>480016</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>563019</t>
+          <t>566644</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>709191</t>
+          <t>707644</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>810407</t>
+          <t>816482</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3147745</t>
+          <t>3143426</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3212066</t>
+          <t>3207626</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2985106</t>
+          <t>2981481</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3072648</t>
+          <t>3068109</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6157637</t>
+          <t>6151562</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6258853</t>
+          <t>6260400</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,84%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2016</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12346</t>
+          <t>13065</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31770</t>
+          <t>32176</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15714</t>
+          <t>15479</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35514</t>
+          <t>34855</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33601</t>
+          <t>32205</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58991</t>
+          <t>59862</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>397322</t>
+          <t>396916</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>416746</t>
+          <t>416027</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>311541</t>
+          <t>312200</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>331341</t>
+          <t>331576</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>717156</t>
+          <t>716285</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>742546</t>
+          <t>743942</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11302</t>
+          <t>11799</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29618</t>
+          <t>28824</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14756</t>
+          <t>15471</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34826</t>
+          <t>36439</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30092</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57186</t>
+          <t>60419</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>347609</t>
+          <t>348403</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>365925</t>
+          <t>365428</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>337447</t>
+          <t>335834</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>357517</t>
+          <t>356802</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>692314</t>
+          <t>689081</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>719408</t>
+          <t>718602</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26055</t>
+          <t>25852</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50770</t>
+          <t>49223</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14241</t>
+          <t>14430</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33261</t>
+          <t>34434</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45773</t>
+          <t>44660</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74461</t>
+          <t>75936</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>471144</t>
+          <t>472691</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>495859</t>
+          <t>496062</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132862</t>
+          <t>131689</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151882</t>
+          <t>151693</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>613575</t>
+          <t>612100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>642263</t>
+          <t>643376</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52232</t>
+          <t>52579</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84353</t>
+          <t>84693</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79185</t>
+          <t>80996</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118187</t>
+          <t>118702</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>139863</t>
+          <t>142214</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>191272</t>
+          <t>189236</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1065285</t>
+          <t>1064945</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1097406</t>
+          <t>1097059</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>707689</t>
+          <t>707174</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>746691</t>
+          <t>744880</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1784242</t>
+          <t>1786278</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1835651</t>
+          <t>1833300</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39248</t>
+          <t>40051</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67694</t>
+          <t>67423</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>103347</t>
+          <t>104007</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142843</t>
+          <t>145909</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>149070</t>
+          <t>151259</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>202181</t>
+          <t>205677</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>553012</t>
+          <t>553283</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>581458</t>
+          <t>580655</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>595401</t>
+          <t>592335</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>634897</t>
+          <t>634237</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1156769</t>
+          <t>1153273</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1209880</t>
+          <t>1207691</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,87%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19139</t>
+          <t>18934</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>119942</t>
+          <t>117850</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>166642</t>
+          <t>165706</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>128306</t>
+          <t>127484</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>177445</t>
+          <t>176621</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>268006</t>
+          <t>268211</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>281970</t>
+          <t>281652</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>915383</t>
+          <t>916319</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>962083</t>
+          <t>964175</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1191725</t>
+          <t>1192549</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1240864</t>
+          <t>1241686</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>179466</t>
+          <t>176700</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>237155</t>
+          <t>237834</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>390309</t>
+          <t>393378</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>472640</t>
+          <t>473080</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>588485</t>
+          <t>586610</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>688510</t>
+          <t>690946</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3148567</t>
+          <t>3147888</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3206256</t>
+          <t>3209022</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3058956</t>
+          <t>3058516</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3141287</t>
+          <t>3138218</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6228808</t>
+          <t>6226372</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6328833</t>
+          <t>6330708</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,52%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2023</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19171</t>
+          <t>18893</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44228</t>
+          <t>43804</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24662</t>
+          <t>23976</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44455</t>
+          <t>43581</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48544</t>
+          <t>47528</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81775</t>
+          <t>78710</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>460984</t>
+          <t>461408</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>486041</t>
+          <t>486319</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>403012</t>
+          <t>403886</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>422805</t>
+          <t>423491</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>870904</t>
+          <t>873969</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>904135</t>
+          <t>905151</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>6752</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21048</t>
+          <t>20430</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26456</t>
+          <t>26156</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47908</t>
+          <t>46354</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36147</t>
+          <t>35689</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62195</t>
+          <t>61451</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>431165</t>
+          <t>431783</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>445672</t>
+          <t>445461</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>334672</t>
+          <t>336226</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>356124</t>
+          <t>356424</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>772598</t>
+          <t>773342</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>798646</t>
+          <t>799104</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10281</t>
+          <t>11945</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59679</t>
+          <t>61721</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13026</t>
+          <t>12772</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25513</t>
+          <t>25394</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21330</t>
+          <t>22832</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80756</t>
+          <t>80667</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>608585</t>
+          <t>606543</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>657983</t>
+          <t>656319</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141398</t>
+          <t>141517</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153885</t>
+          <t>154139</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>754419</t>
+          <t>754508</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>813845</t>
+          <t>812343</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53638</t>
+          <t>52512</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84644</t>
+          <t>83380</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37432</t>
+          <t>35666</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89556</t>
+          <t>90400</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94828</t>
+          <t>92206</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>158442</t>
+          <t>159235</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>948968</t>
+          <t>950232</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>979974</t>
+          <t>981100</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>887571</t>
+          <t>886727</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>939695</t>
+          <t>941461</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1852298</t>
+          <t>1851505</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1915912</t>
+          <t>1918534</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29426</t>
+          <t>29713</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53118</t>
+          <t>52519</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>81456</t>
+          <t>85008</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>134156</t>
+          <t>136797</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124892</t>
+          <t>124255</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>178925</t>
+          <t>178924</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>421928</t>
+          <t>422527</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>445620</t>
+          <t>445333</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>706620</t>
+          <t>703979</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>759320</t>
+          <t>755768</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1136896</t>
+          <t>1136897</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1190929</t>
+          <t>1191566</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,56%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23393</t>
+          <t>23052</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>100021</t>
+          <t>99738</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>133904</t>
+          <t>137096</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>107098</t>
+          <t>106376</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>146485</t>
+          <t>146343</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>217114</t>
+          <t>217455</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236510</t>
+          <t>236713</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>626635</t>
+          <t>623443</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>660518</t>
+          <t>660801</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>854561</t>
+          <t>854703</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>893948</t>
+          <t>894670</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,37%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>151303</t>
+          <t>144787</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>224662</t>
+          <t>220855</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>303002</t>
+          <t>311978</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>423596</t>
+          <t>424553</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>487237</t>
+          <t>495547</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>629008</t>
+          <t>629145</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3150192</t>
+          <t>3153999</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3223551</t>
+          <t>3230067</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3151803</t>
+          <t>3150846</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3272397</t>
+          <t>3263421</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6321246</t>
+          <t>6321109</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6463017</t>
+          <t>6454707</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,87%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1001-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1001-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13074</t>
+          <t>12736</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31456</t>
+          <t>31771</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13447</t>
+          <t>13903</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30858</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30018</t>
+          <t>30016</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55516</t>
+          <t>54477</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>442320</t>
+          <t>442005</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>460702</t>
+          <t>461040</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>275822</t>
+          <t>276227</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>293233</t>
+          <t>292777</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>724941</t>
+          <t>725980</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>750439</t>
+          <t>750441</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9474</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26445</t>
+          <t>26324</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21775</t>
+          <t>22166</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43064</t>
+          <t>44037</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34550</t>
+          <t>34694</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62108</t>
+          <t>61794</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>340489</t>
+          <t>340610</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>357460</t>
+          <t>358481</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>328801</t>
+          <t>327828</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>350090</t>
+          <t>349699</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>676691</t>
+          <t>677005</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>704249</t>
+          <t>704105</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24064</t>
+          <t>23069</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46234</t>
+          <t>45391</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11943</t>
+          <t>10963</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>27927</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39920</t>
+          <t>40251</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66705</t>
+          <t>68746</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>496155</t>
+          <t>496998</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>518325</t>
+          <t>519320</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>139224</t>
+          <t>139855</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155839</t>
+          <t>156819</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643466</t>
+          <t>641425</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>670251</t>
+          <t>669920</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78266</t>
+          <t>76930</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>116088</t>
+          <t>114800</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53179</t>
+          <t>54557</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85136</t>
+          <t>85787</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>140323</t>
+          <t>141369</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>188045</t>
+          <t>191853</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1122246</t>
+          <t>1123534</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1160068</t>
+          <t>1161404</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>629149</t>
+          <t>628498</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>661106</t>
+          <t>659728</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1764575</t>
+          <t>1760767</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1812297</t>
+          <t>1811251</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13609</t>
+          <t>13714</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32178</t>
+          <t>33225</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41441</t>
+          <t>42962</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70328</t>
+          <t>71331</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60605</t>
+          <t>60905</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96219</t>
+          <t>98499</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>318377</t>
+          <t>317330</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>336946</t>
+          <t>336841</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>498424</t>
+          <t>497421</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>527311</t>
+          <t>525790</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>823088</t>
+          <t>820808</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>858702</t>
+          <t>858402</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,37%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19383</t>
+          <t>19341</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>99427</t>
+          <t>100788</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>141364</t>
+          <t>142162</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>110534</t>
+          <t>110126</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>154325</t>
+          <t>156320</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>278818</t>
+          <t>278860</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>292513</t>
+          <t>292783</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1107396</t>
+          <t>1106598</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1149333</t>
+          <t>1147972</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1392635</t>
+          <t>1390640</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1436426</t>
+          <t>1436834</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,88%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>171777</t>
+          <t>171066</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>227853</t>
+          <t>225922</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>286896</t>
+          <t>281833</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>356246</t>
+          <t>352274</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,47 +2841,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>8,34%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>10,43%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>515440</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>472935</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>564735</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>7,75%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>7,11%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>8,49%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>10,55%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>515440</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>475504</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>559871</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>7,15%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3042337</t>
+          <t>3044268</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3098413</t>
+          <t>3099124</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3021878</t>
+          <t>3025850</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3091228</t>
+          <t>3096291</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,47 +2954,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>91,66%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>6132874</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>6083579</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>6175379</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>92,25%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>91,51%</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>6132874</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>6088443</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>6172810</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>92,25%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>91,58%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,89%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10739</t>
+          <t>10995</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29620</t>
+          <t>29939</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>15003</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34800</t>
+          <t>35104</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29572</t>
+          <t>29993</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56562</t>
+          <t>56256</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>406654</t>
+          <t>406335</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425535</t>
+          <t>425279</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>279654</t>
+          <t>279350</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>300003</t>
+          <t>299451</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>694166</t>
+          <t>694472</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>721156</t>
+          <t>720735</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18692</t>
+          <t>16516</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41938</t>
+          <t>39996</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20938</t>
+          <t>20438</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43422</t>
+          <t>42378</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42931</t>
+          <t>42696</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73099</t>
+          <t>76497</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>376859</t>
+          <t>378801</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>400105</t>
+          <t>402281</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>294589</t>
+          <t>295633</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>317073</t>
+          <t>317573</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>683709</t>
+          <t>680311</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713877</t>
+          <t>714112</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39553</t>
+          <t>38802</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70731</t>
+          <t>69046</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35764</t>
+          <t>34345</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61219</t>
+          <t>60718</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81917</t>
+          <t>80946</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>121799</t>
+          <t>122832</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>558684</t>
+          <t>560369</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>589862</t>
+          <t>590613</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>198910</t>
+          <t>199411</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>224365</t>
+          <t>225784</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>767745</t>
+          <t>766712</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>807627</t>
+          <t>808598</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,9%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85428</t>
+          <t>83774</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127164</t>
+          <t>123802</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76133</t>
+          <t>76770</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114327</t>
+          <t>113803</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>170750</t>
+          <t>171834</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>228417</t>
+          <t>230918</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1031845</t>
+          <t>1035207</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1073581</t>
+          <t>1075235</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>652330</t>
+          <t>652854</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>690524</t>
+          <t>689887</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1697250</t>
+          <t>1694749</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1754917</t>
+          <t>1753833</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,08%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19142</t>
+          <t>19362</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40941</t>
+          <t>41658</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>129036</t>
+          <t>132705</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>175414</t>
+          <t>175919</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>156990</t>
+          <t>159535</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>210670</t>
+          <t>209053</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>468601</t>
+          <t>467884</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>490400</t>
+          <t>490180</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>584108</t>
+          <t>583603</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>630486</t>
+          <t>626817</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1058394</t>
+          <t>1060011</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1112074</t>
+          <t>1109529</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,43%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4803</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18039</t>
+          <t>17658</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>150615</t>
+          <t>150033</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>197665</t>
+          <t>200120</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>157293</t>
+          <t>159066</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>206974</t>
+          <t>208567</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248843</t>
+          <t>249224</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262062</t>
+          <t>262079</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>911686</t>
+          <t>909231</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>958736</t>
+          <t>959318</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1169259</t>
+          <t>1167666</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1218940</t>
+          <t>1217167</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,44%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>212293</t>
+          <t>211748</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>276493</t>
+          <t>273407</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>480016</t>
+          <t>479102</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>566644</t>
+          <t>565452</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>707644</t>
+          <t>705372</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>816482</t>
+          <t>812996</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3143426</t>
+          <t>3146512</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3207626</t>
+          <t>3208171</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2981481</t>
+          <t>2982673</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3068109</t>
+          <t>3069023</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6151562</t>
+          <t>6155048</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6260400</t>
+          <t>6262672</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,88%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13065</t>
+          <t>13056</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32176</t>
+          <t>31390</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15479</t>
+          <t>14984</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34855</t>
+          <t>34747</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32205</t>
+          <t>32611</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59862</t>
+          <t>58874</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>396916</t>
+          <t>397702</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>416027</t>
+          <t>416036</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>312200</t>
+          <t>312308</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>331576</t>
+          <t>332071</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>716285</t>
+          <t>717273</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>743942</t>
+          <t>743536</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,8%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11799</t>
+          <t>12019</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28824</t>
+          <t>30603</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15471</t>
+          <t>15125</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36439</t>
+          <t>36369</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,47 +6396,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>9,77%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>42942</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>31166</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>58813</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>5,73%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>4,16%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>9,79%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>42942</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>30898</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>60419</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>348403</t>
+          <t>346624</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>365428</t>
+          <t>365208</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>335834</t>
+          <t>335904</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>356802</t>
+          <t>357148</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,47 +6509,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>95,94%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>706558</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>690687</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>718334</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>94,27%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>92,15%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>95,84%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>706558</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>689081</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>718602</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>94,27%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>91,94%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25852</t>
+          <t>25076</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49223</t>
+          <t>49001</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14430</t>
+          <t>13928</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34434</t>
+          <t>34828</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44660</t>
+          <t>45495</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75936</t>
+          <t>77283</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>472691</t>
+          <t>472913</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>496062</t>
+          <t>496838</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131689</t>
+          <t>131295</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151693</t>
+          <t>152195</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>612100</t>
+          <t>610753</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>643376</t>
+          <t>642541</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52579</t>
+          <t>53424</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84693</t>
+          <t>86602</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80996</t>
+          <t>77825</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118702</t>
+          <t>116495</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>142214</t>
+          <t>143647</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>189236</t>
+          <t>191285</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1064945</t>
+          <t>1063036</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1097059</t>
+          <t>1096214</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>707174</t>
+          <t>709381</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>744880</t>
+          <t>748051</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1786278</t>
+          <t>1784229</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1833300</t>
+          <t>1831867</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40051</t>
+          <t>40184</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67423</t>
+          <t>68008</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>104007</t>
+          <t>103170</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>145909</t>
+          <t>144966</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>151259</t>
+          <t>150932</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>205677</t>
+          <t>199603</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>553283</t>
+          <t>552698</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>580655</t>
+          <t>580522</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>592335</t>
+          <t>593278</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>634237</t>
+          <t>635074</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1153273</t>
+          <t>1159347</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1207691</t>
+          <t>1208018</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,89%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>5509</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18934</t>
+          <t>19742</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>117850</t>
+          <t>119128</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>165706</t>
+          <t>165937</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>127484</t>
+          <t>128349</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>176621</t>
+          <t>177013</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>268211</t>
+          <t>267403</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>281652</t>
+          <t>281636</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>916319</t>
+          <t>916088</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>964175</t>
+          <t>962897</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1192549</t>
+          <t>1192157</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1241686</t>
+          <t>1240821</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,63%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>176700</t>
+          <t>178125</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>237834</t>
+          <t>236890</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>393378</t>
+          <t>394045</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>473080</t>
+          <t>476814</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>586610</t>
+          <t>590219</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>690946</t>
+          <t>693200</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3147888</t>
+          <t>3148832</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3209022</t>
+          <t>3207597</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3058516</t>
+          <t>3054782</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3138218</t>
+          <t>3137551</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6226372</t>
+          <t>6224118</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6330708</t>
+          <t>6327099</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28269</t>
+          <t>28784</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18893</t>
+          <t>18726</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43804</t>
+          <t>43108</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>33268</t>
+          <t>37413</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23976</t>
+          <t>28197</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43581</t>
+          <t>49855</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>61537</t>
+          <t>66196</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47528</t>
+          <t>51940</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78710</t>
+          <t>84855</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>476943</t>
+          <t>521834</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>461408</t>
+          <t>507510</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>486319</t>
+          <t>531892</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>414199</t>
+          <t>450998</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>403886</t>
+          <t>438556</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>423491</t>
+          <t>460214</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>891142</t>
+          <t>972833</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>873969</t>
+          <t>954174</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>905151</t>
+          <t>987089</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11788</t>
+          <t>13361</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>7798</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20430</t>
+          <t>23073</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35430</t>
+          <t>40874</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26156</t>
+          <t>30963</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46354</t>
+          <t>53212</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>47218</t>
+          <t>54235</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35689</t>
+          <t>41749</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61451</t>
+          <t>68386</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>440425</t>
+          <t>469851</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>431783</t>
+          <t>460139</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>445461</t>
+          <t>475414</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>347150</t>
+          <t>382269</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>336226</t>
+          <t>369931</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>356424</t>
+          <t>392180</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>787575</t>
+          <t>852120</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>773342</t>
+          <t>837969</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>799104</t>
+          <t>864606</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>34804</t>
+          <t>35782</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11945</t>
+          <t>24423</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61721</t>
+          <t>49985</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17827</t>
+          <t>20168</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12772</t>
+          <t>14246</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25394</t>
+          <t>27743</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>52631</t>
+          <t>55949</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22832</t>
+          <t>44555</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80667</t>
+          <t>71062</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>633460</t>
+          <t>435830</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>606543</t>
+          <t>421627</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>656319</t>
+          <t>447189</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>149084</t>
+          <t>167329</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141517</t>
+          <t>159754</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154139</t>
+          <t>173251</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>782544</t>
+          <t>603160</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>754508</t>
+          <t>588047</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>812343</t>
+          <t>614554</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>67008</t>
+          <t>73683</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52512</t>
+          <t>58923</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83380</t>
+          <t>90141</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>67070</t>
+          <t>74662</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35666</t>
+          <t>60924</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90400</t>
+          <t>89116</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>134078</t>
+          <t>148345</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92206</t>
+          <t>129146</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>159235</t>
+          <t>171813</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>966604</t>
+          <t>1056958</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>950232</t>
+          <t>1040500</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>981100</t>
+          <t>1071718</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>910057</t>
+          <t>785540</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>886727</t>
+          <t>771086</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>941461</t>
+          <t>799278</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1876662</t>
+          <t>1842498</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1851505</t>
+          <t>1819030</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1918534</t>
+          <t>1861697</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1033612</t>
+          <t>1130641</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1033612</t>
+          <t>1130641</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1033612</t>
+          <t>1130641</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977127</t>
+          <t>860202</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977127</t>
+          <t>860202</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977127</t>
+          <t>860202</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2010740</t>
+          <t>1990843</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2010740</t>
+          <t>1990843</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2010740</t>
+          <t>1990843</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>39610</t>
+          <t>42204</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29713</t>
+          <t>31486</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52519</t>
+          <t>56597</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>112701</t>
+          <t>121803</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>85008</t>
+          <t>106939</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>136797</t>
+          <t>141133</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>152311</t>
+          <t>164008</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124255</t>
+          <t>142677</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>178924</t>
+          <t>184509</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>435436</t>
+          <t>525760</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>422527</t>
+          <t>511367</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>445333</t>
+          <t>536478</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>728075</t>
+          <t>708486</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>703979</t>
+          <t>689156</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>755768</t>
+          <t>723350</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1163510</t>
+          <t>1234244</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1136897</t>
+          <t>1213743</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1191566</t>
+          <t>1255575</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>89,8%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>840776</t>
+          <t>830289</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>840776</t>
+          <t>830289</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>840776</t>
+          <t>830289</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1315821</t>
+          <t>1398252</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1315821</t>
+          <t>1398252</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1315821</t>
+          <t>1398252</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9156</t>
+          <t>10697</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23052</t>
+          <t>24197</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>115987</t>
+          <t>125763</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>99738</t>
+          <t>108098</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>137096</t>
+          <t>146015</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>125143</t>
+          <t>136460</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>106376</t>
+          <t>117387</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>146343</t>
+          <t>161803</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>231351</t>
+          <t>226531</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>217455</t>
+          <t>213031</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236713</t>
+          <t>232325</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>644552</t>
+          <t>717643</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>623443</t>
+          <t>697391</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>660801</t>
+          <t>735308</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>875903</t>
+          <t>944173</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>854703</t>
+          <t>918830</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>894670</t>
+          <t>963246</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,14%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760539</t>
+          <t>843406</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760539</t>
+          <t>843406</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760539</t>
+          <t>843406</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001046</t>
+          <t>1080633</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001046</t>
+          <t>1080633</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001046</t>
+          <t>1080633</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>190636</t>
+          <t>204511</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>144787</t>
+          <t>180278</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>220855</t>
+          <t>236629</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>382283</t>
+          <t>420683</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>311978</t>
+          <t>387174</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>424553</t>
+          <t>454791</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>572919</t>
+          <t>625194</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>495547</t>
+          <t>578299</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>629145</t>
+          <t>668383</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3184218</t>
+          <t>3236763</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3153999</t>
+          <t>3204645</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3230067</t>
+          <t>3260996</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3193116</t>
+          <t>3212264</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3150846</t>
+          <t>3178156</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3263421</t>
+          <t>3245773</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6377335</t>
+          <t>6449027</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6321109</t>
+          <t>6405838</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6454707</t>
+          <t>6495922</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3374854</t>
+          <t>3441274</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3374854</t>
+          <t>3441274</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3374854</t>
+          <t>3441274</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3575399</t>
+          <t>3632947</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3575399</t>
+          <t>3632947</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3575399</t>
+          <t>3632947</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6950254</t>
+          <t>7074221</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6950254</t>
+          <t>7074221</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6950254</t>
+          <t>7074221</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
